--- a/Shorthand Notes.xlsx
+++ b/Shorthand Notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/46a2e6c38b4231b1/History/0. Public/Blender project/User's exp/00. Presets Relevant/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FaustK\Documents\GitHub\Mograph-Presets-of-Geometry-Nodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="11_F25DC773A252ABDACC1048DFD1997CD25BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F36B5066-6F8A-4C75-9017-8569478D8A53}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305270DD-9D45-4933-B70C-A3E4198C94B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="555" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>Node Name</t>
   </si>
@@ -142,6 +142,15 @@
   </si>
   <si>
     <t>gsetg</t>
+  </si>
+  <si>
+    <t>G_Random Value</t>
+  </si>
+  <si>
+    <t>gre1</t>
+  </si>
+  <si>
+    <t>G_Remap 0-1</t>
   </si>
 </sst>
 </file>
@@ -459,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -549,7 +558,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -557,26 +566,26 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
         <v>31</v>
@@ -584,41 +593,57 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>35</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>28</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B22" t="s">
         <v>27</v>
       </c>
     </row>

--- a/Shorthand Notes.xlsx
+++ b/Shorthand Notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FaustK\Documents\GitHub\Mograph-Presets-of-Geometry-Nodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305270DD-9D45-4933-B70C-A3E4198C94B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7739A623-9A0F-4E9F-8CFD-DA50CF37AD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="555" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3405" yWindow="3555" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>Node Name</t>
   </si>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>G_Remap 0-1</t>
+  </si>
+  <si>
+    <t>G_Curve to Mesh</t>
+  </si>
+  <si>
+    <t>gctt</t>
   </si>
 </sst>
 </file>
@@ -468,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -534,39 +540,39 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -574,18 +580,18 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
         <v>31</v>
@@ -593,57 +599,65 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>41</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>28</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>27</v>
       </c>
     </row>
